--- a/output/pdf_financials_xlsx/PURR.xlsx
+++ b/output/pdf_financials_xlsx/PURR.xlsx
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>1.149051</v>
+        <v>0.829752</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>2.277775</v>
+        <v>2.148884</v>
       </c>
     </row>
     <row r="119">
@@ -3030,7 +3030,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>-0.319299</v>
       </c>

--- a/output/pdf_financials_xlsx/PURR.xlsx
+++ b/output/pdf_financials_xlsx/PURR.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.71862</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002506</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.71862</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002506</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.426824</v>
+        <v>0.7082039999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.150972</v>
+        <v>0.148466</v>
       </c>
     </row>
     <row r="49">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
